--- a/backend/template/test_case_export_template.xlsx
+++ b/backend/template/test_case_export_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28180" windowHeight="14020"/>
+    <workbookView windowWidth="26860" windowHeight="14500"/>
   </bookViews>
   <sheets>
     <sheet name="SwRD_001" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>测试用例标识</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>功能性测试</t>
+  </si>
+  <si>
+    <t>用例场景</t>
+  </si>
+  <si>
+    <t>正常流程用例</t>
   </si>
   <si>
     <t>测试步骤</t>
@@ -847,7 +853,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -875,20 +881,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1415,7 +1430,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="24.7692307692308" customWidth="1"/>
@@ -1424,7 +1439,7 @@
     <col min="4" max="4" width="32.1538461538462" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" spans="1:6">
+    <row r="1" ht="17" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1434,7 +1449,7 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" ht="17" spans="1:6">
+    <row r="2" ht="17" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1444,7 +1459,7 @@
       <c r="C2" s="4"/>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" ht="17" spans="1:6">
+    <row r="3" ht="17" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1454,7 +1469,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" ht="17" spans="1:6">
+    <row r="4" ht="17" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1464,7 +1479,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" ht="17" spans="1:6">
+    <row r="5" ht="17" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1474,89 +1489,100 @@
       <c r="C5" s="7"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" ht="51" spans="1:6">
+    <row r="6" ht="17" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
+    </row>
+    <row r="7" ht="51" spans="1:4">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="7" ht="17" spans="1:6">
-      <c r="A7" s="2">
+    <row r="8" ht="17" spans="1:4">
+      <c r="A8" s="2">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="8" ht="84" spans="1:6">
-      <c r="A8" s="2">
+    <row r="9" ht="84" spans="1:6">
+      <c r="A9" s="2">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="F8" s="10"/>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="F9" s="16"/>
     </row>
-    <row r="9" ht="68" spans="1:6">
-      <c r="A9" s="2">
+    <row r="10" ht="68" spans="1:4">
+      <c r="A10" s="2">
         <v>3</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="9"/>
+      <c r="B10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="12"/>
     </row>
-    <row r="10" ht="84" spans="1:6">
-      <c r="A10" s="2">
+    <row r="11" ht="84" spans="1:4">
+      <c r="A11" s="2">
         <v>4</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B11" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="9"/>
+      <c r="D11" s="12"/>
     </row>
-    <row r="11" ht="34" spans="1:6">
-      <c r="A11" s="2">
+    <row r="12" ht="34" spans="1:4">
+      <c r="A12" s="2">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="9"/>
+      <c r="B12" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="D8:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
